--- a/evidencias/pruebas/api/orden-OS-001-2026.xlsx
+++ b/evidencias/pruebas/api/orden-OS-001-2026.xlsx
@@ -100,7 +100,7 @@
     <t>FECHA ORDEN</t>
   </si>
   <si>
-    <t>05/10/2026</t>
+    <t>06/10/2026</t>
   </si>
   <si>
     <t>#</t>
